--- a/artfynd/A 29576-2024 artfynd.xlsx
+++ b/artfynd/A 29576-2024 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83571831</v>
+        <v>17107138</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Vg</t>
+          <t>Svenljunga kommun, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397933.6695867102</v>
+        <v>397934</v>
       </c>
       <c r="R2" t="n">
-        <v>6376962.626709091</v>
+        <v>6376963</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +738,14 @@
           <t>Tranemo</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>9870CB23-328D-4ECA-9C86-12E28957E85D</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>{3BD476F0-F694-465C-B72A-6E6157B637D0}</t>
+          <t>2012-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,72 +757,76 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Peter Nolbrant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Stenström, Peter Nolbrant</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17107138</v>
+        <v>83571831</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svenljunga kommun, Vg</t>
+          <t>Ask (Skyddsvärt träd), Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397933.6695867102</v>
+        <v>397934</v>
       </c>
       <c r="R3" t="n">
-        <v>6376962.626709091</v>
+        <v>6376963</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,24 +848,24 @@
           <t>Tranemo</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9870CB23-328D-4ECA-9C86-12E28957E85D</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-03-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>{3BD476F0-F694-465C-B72A-6E6157B637D0}</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,25 +877,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Peter Nolbrant</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Anna Stenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Anna Stenström, Peter Nolbrant</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Inventering skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 29576-2024 artfynd.xlsx
+++ b/artfynd/A 29576-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17107138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,8 +903,17 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571831</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>